--- a/output/pdf_financials_xlsx/KDA.xlsx
+++ b/output/pdf_financials_xlsx/KDA.xlsx
@@ -1951,19 +1951,19 @@
         <v>0.510003</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.164143</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.28983</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.411782</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.233334</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.78223</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>1.71715</v>
@@ -2037,19 +2037,19 @@
         <v>0.510003</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.164143</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.28983</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.411782</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.233334</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.78223</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.71715</v>
@@ -2553,19 +2553,19 @@
         <v>0.146489</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.450901</v>
+        <v>0.286758</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.801957</v>
+        <v>1.512127</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.313751</v>
+        <v>0.901969</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.316884</v>
+        <v>1.08355</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.360273</v>
+        <v>0.578043</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.346747</v>
@@ -5864,7 +5864,7 @@
         <v>-2.134391</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>-7.973126</v>
+        <v>-12.480721</v>
       </c>
       <c r="L124" s="3" t="n">
         <v>-0.837117</v>
@@ -5907,7 +5907,7 @@
         <v>-2.134391</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>-7.973126</v>
+        <v>-12.480721</v>
       </c>
       <c r="L125" s="3" t="n">
         <v>-0.837117</v>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">

--- a/output/pdf_financials_xlsx/KDA.xlsx
+++ b/output/pdf_financials_xlsx/KDA.xlsx
@@ -940,22 +940,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0</v>
+        <v>0.003175</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.056515</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>-0.247304</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>0.636431</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>-1.220348</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>-4.48862</v>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
@@ -1658,22 +1658,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.892744</v>
+        <v>0.8895690000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.170759</v>
+        <v>-1.114244</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.640351</v>
+        <v>-1.393047</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-8.801895</v>
+        <v>-9.438326</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.512818</v>
+        <v>0.70753</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-7.437932</v>
+        <v>-2.949312</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1705,22 +1705,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.003523</v>
+        <v>0.007625</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.06908</v>
+        <v>0.07413599999999999</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.472646</v>
+        <v>0.487822</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1.341785</v>
+        <v>1.39288</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.372136</v>
+        <v>0.817276</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.481871</v>
+        <v>0.5158779999999999</v>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
@@ -1750,22 +1750,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.896267</v>
+        <v>0.897194</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.101679</v>
+        <v>-1.040108</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.167705</v>
+        <v>-0.9052249999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.46011</v>
+        <v>-8.045446</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.859318</v>
+        <v>1.524806</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-6.956061</v>
+        <v>-2.433434</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1797,22 +1797,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>23.60335942184783</v>
+        <v>23.6277721405846</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-19.96940636604255</v>
+        <v>-18.85334958419993</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-14.69432548779427</v>
+        <v>-11.39129385391736</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-25.1894294826917</v>
+        <v>-27.16584536606083</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>4.209817865626389</v>
+        <v>7.470058279256703</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-30.1208673642528</v>
+        <v>-10.5371621602604</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -4799,28 +4799,28 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.004103</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.07413599999999999</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.487822</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>1.39288</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>1.425982</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.576403</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.8346209999999999</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0.480422</v>
+        <v>0.480423</v>
       </c>
       <c r="J100" s="3" t="n">
         <v>0.625177</v>
@@ -22924,7 +22924,11 @@
           <t>Additions to intangibles assets (note 8)</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -24802,7 +24806,11 @@
           <t>Additions to intangibles assets (note 9)</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -25108,7 +25116,11 @@
           <t>Additions to intangibles assets (note 9)</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -27304,7 +27316,11 @@
           <t>Additions to intangibles assets (note 7)</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -29166,7 +29182,11 @@
           <t>Depreciation of property and equipment (note 7)</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -29240,7 +29260,11 @@
           <t>Depreciation of right of use assets (note 10)</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -29316,7 +29340,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -30126,7 +30150,11 @@
           <t>Additions to intangibles assets (note 8)</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -31168,7 +31196,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -31244,7 +31276,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -32290,7 +32322,11 @@
           <t>Additions to intangible assets 9</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E343" s="5" t="n">
         <v>-0.00374</v>
       </c>
@@ -33426,7 +33462,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -33502,7 +33542,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -34332,7 +34372,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -35324,7 +35368,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -35400,7 +35448,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -36006,7 +36054,11 @@
           <t>Additions to intangible assets 7</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -37066,7 +37118,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -37142,7 +37198,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -37676,7 +37732,11 @@
           <t>Additions to intangible assets 10</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -39200,7 +39260,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E434" s="5" t="n">
         <v>0.004103</v>
       </c>
@@ -50512,7 +50576,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D585" t="inlineStr"/>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E585" t="inlineStr">
         <is>
           <t>-</t>
@@ -50588,7 +50656,7 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
@@ -50738,7 +50806,11 @@
           <t>Net finance costs 20</t>
         </is>
       </c>
-      <c r="D588" t="inlineStr"/>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E588" t="inlineStr">
         <is>
           <t>-</t>
@@ -52100,7 +52172,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D606" t="inlineStr"/>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E606" t="inlineStr">
         <is>
           <t>-</t>
@@ -52176,7 +52252,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -53690,7 +53766,11 @@
           <t>Depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D627" t="inlineStr"/>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E627" t="inlineStr">
         <is>
           <t>-</t>
@@ -53766,7 +53846,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -53916,7 +53996,11 @@
           <t>Net finance costs 19</t>
         </is>
       </c>
-      <c r="D630" t="inlineStr"/>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E630" t="inlineStr">
         <is>
           <t>-</t>
@@ -55026,7 +55110,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D645" t="inlineStr"/>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E645" t="inlineStr">
         <is>
           <t>-</t>
@@ -55098,7 +55186,7 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
@@ -55380,7 +55468,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D650" t="inlineStr"/>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E650" s="5" t="n">
         <v>-0.003175</v>
       </c>
@@ -57168,7 +57260,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D674" t="inlineStr"/>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E674" s="5" t="n">
         <v>0.004102</v>
       </c>
@@ -57240,7 +57336,7 @@
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E675" s="5" t="n">

--- a/output/pdf_financials_xlsx/KDA.xlsx
+++ b/output/pdf_financials_xlsx/KDA.xlsx
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.276465</v>
+        <v>1.22723</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-4.074216</v>
+        <v>-9.208652000000001</v>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>0.9052249999999999</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>8.045446</v>
+        <v>0.695311</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0.002407</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0.391104</v>
+        <v>-0.341869</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0.488112</v>
+        <v>4.646324</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0</v>
@@ -1313,10 +1313,10 @@
         <v>-8.106584</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-5.295416</v>
+        <v>-0.521004</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-8.858589</v>
+        <v>-8.322082</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-4.774412</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>-0.536507</v>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-0.323827</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.276465</v>
+        <v>1.22723</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-4.074216</v>
+        <v>-9.208652000000001</v>
       </c>
       <c r="K27" s="1" t="inlineStr">
         <is>
@@ -1773,10 +1773,10 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.756887</v>
+        <v>1.707652</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.449039</v>
+        <v>-8.583475</v>
       </c>
       <c r="K29" s="1" t="inlineStr">
         <is>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>7.209605831612581</v>
+        <v>7.007563843072939</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-11.96598742097169</v>
+        <v>-29.77923818148329</v>
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>-55.1848354407075</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-91.40583931073934</v>
+        <v>-7.899560265147448</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0.4693672998997695</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>30.63961800754427</v>
+        <v>27.85696242758081</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-11.98051355156428</v>
+        <v>-50.45607109487903</v>
       </c>
       <c r="K31" s="1" t="inlineStr">
         <is>
@@ -2206,13 +2206,13 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.216294</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.034853</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.296778</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>0</v>
@@ -2249,13 +2249,13 @@
         <v>0.407184</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1.43852</v>
+        <v>1.654814</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>1.365559</v>
+        <v>1.400412</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>7.345498</v>
+        <v>7.642276</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>3.394855</v>
@@ -2550,13 +2550,13 @@
         <v>0.127607</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.146489</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.286758</v>
+        <v>0.251905</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.512127</v>
+        <v>1.215349</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.901969</v>
@@ -5152,13 +5152,13 @@
         <v>0</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>6.685</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>0</v>
+        <v>2.295652</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>0</v>
+        <v>0.602677</v>
       </c>
       <c r="H108" s="3" t="n">
         <v>0</v>
@@ -22248,7 +22248,11 @@
           <t>Deferred income tax expenses</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -24048,7 +24052,11 @@
           <t>Deferred income tax expenses (note 19)</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -25956,7 +25964,11 @@
           <t>Deferred income tax expenses (recovery) (note 20)</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -27608,7 +27620,11 @@
           <t>Proceeds from share issued</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -28726,7 +28742,11 @@
           <t>Deferred income tax expenses (recovery) (note 21)</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -31120,7 +31140,11 @@
           <t>Deferred income tax expense 13</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -31352,7 +31376,11 @@
           <t>Impairment charges 9</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -32932,7 +32960,11 @@
           <t>Proceeds from unclosed private placement</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -33618,7 +33650,11 @@
           <t>Impairment charges 8</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -33922,7 +33958,11 @@
           <t>Deferred income tax expense recovery 12</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
@@ -35524,7 +35564,11 @@
           <t>Impairment charges 7</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -35676,7 +35720,11 @@
           <t>Deferred income tax (recovery)</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -41844,7 +41892,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E468" t="inlineStr">
         <is>
           <t>-</t>
@@ -44828,7 +44880,11 @@
           <t>(Loss) income before income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E508" t="inlineStr">
         <is>
           <t>-</t>
@@ -44980,7 +45036,11 @@
           <t>Deferred income tax recovery (note 20)</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E510" t="inlineStr">
         <is>
           <t>-</t>
@@ -45132,7 +45192,11 @@
           <t>Net loss from discontinued operations (note 26)</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E512" t="inlineStr">
         <is>
           <t>-</t>
@@ -51192,7 +51256,11 @@
           <t>Net Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D593" t="inlineStr"/>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E593" t="inlineStr">
         <is>
           <t>-</t>
@@ -51266,7 +51334,11 @@
           <t>Net loss from discontinued operations 5</t>
         </is>
       </c>
-      <c r="D594" t="inlineStr"/>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E594" t="inlineStr">
         <is>
           <t>-</t>
@@ -51494,7 +51566,11 @@
           <t>Deferred income tax recovery 13</t>
         </is>
       </c>
-      <c r="D597" t="inlineStr"/>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E597" t="inlineStr">
         <is>
           <t>-</t>
@@ -52704,7 +52780,11 @@
           <t>Current and deferred income tax recovery 12</t>
         </is>
       </c>
-      <c r="D613" t="inlineStr"/>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E613" t="inlineStr">
         <is>
           <t>-</t>
